--- a/Output/Weekly Scan_14 Jul 2026.xlsx
+++ b/Output/Weekly Scan_14 Jul 2026.xlsx
@@ -509,7 +509,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>57.87</v>
+        <v>58.24</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -541,11 +541,11 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>40.84</v>
+        <v>39.43</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -573,7 +573,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>70.65000000000001</v>
+        <v>67.52</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>50.78</v>
+        <v>53.67</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -637,7 +637,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>45.39</v>
+        <v>47.71</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>57.3</v>
+        <v>55.41</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>48.12</v>
+        <v>50.58</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>65.84999999999999</v>
+        <v>66.31</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>74.53</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>52.16</v>
+        <v>53.98</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>65.59</v>
+        <v>63.36</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>64.22</v>
+        <v>61.81</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>53.89</v>
+        <v>50.51</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>41.22</v>
+        <v>40.63</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>45.98</v>
+        <v>45.03</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>65.65000000000001</v>
+        <v>63.08</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>49.65</v>
+        <v>47.15</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>68.33</v>
+        <v>67.25</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>45.69</v>
+        <v>43.98</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1117,11 +1117,11 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>43.57</v>
+        <v>37.48</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1149,11 +1149,11 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>60.2</v>
+        <v>58.14</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1181,7 +1181,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>54.73</v>
+        <v>54.03</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>53.07</v>
+        <v>52.83</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1245,11 +1245,11 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>59.81</v>
+        <v>60.02</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>72.58</v>
+        <v>69.97</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>55.15</v>
+        <v>58.55</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1341,11 +1341,11 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>61.61</v>
+        <v>59.9</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1373,7 +1373,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>42.33</v>
+        <v>42.61</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>54.57</v>
+        <v>53.72</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>32.15</v>
+        <v>30.79</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>34.11</v>
+        <v>35.5</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>64.17</v>
+        <v>60.3</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>47.16</v>
+        <v>47.3</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>47.3</v>
+        <v>47</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>48.28</v>
+        <v>47.37</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>64.63</v>
+        <v>63.61</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>43.56</v>
+        <v>43.51</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1693,11 +1693,11 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>61.33</v>
+        <v>58.62</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -1725,7 +1725,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>49.12</v>
+        <v>48.15</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>33.38</v>
+        <v>32.49</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>47.97</v>
+        <v>45.87</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>50.11</v>
+        <v>51.19</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>34.81</v>
+        <v>30.29</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>32.93</v>
+        <v>31.68</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>56.25</v>
+        <v>54.59</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>72.23999999999999</v>
+        <v>72.48</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>36.33</v>
+        <v>34.16</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>50.78</v>
+        <v>49.43</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>63.86</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>63.55</v>
+        <v>64.39</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>72.23</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>44.9</v>
+        <v>42.53</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>64.56</v>
+        <v>66.41</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2237,11 +2237,11 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>62.02</v>
+        <v>59.02</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -2269,11 +2269,11 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>63.85</v>
+        <v>59.57</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -2301,7 +2301,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>48.36</v>
+        <v>46.56</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>45.07</v>
+        <v>43.37</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>52.74</v>
+        <v>49.34</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>44.02</v>
+        <v>41.96</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>48.11</v>
+        <v>46.21</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>33.77</v>
+        <v>32.61</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>73.48</v>
+        <v>75.73</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>43.33</v>
+        <v>44.11</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>63.51</v>
+        <v>62.39</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>60.58</v>
+        <v>65.16</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>66.89</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>51.38</v>
+        <v>50.51</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>28.28</v>
+        <v>26.32</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
-        <v>52.99</v>
+        <v>52.25</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>48.92</v>
+        <v>48.55</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
-        <v>67.84999999999999</v>
+        <v>67.03</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
-        <v>61.95</v>
+        <v>60.65</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
-        <v>44.23</v>
+        <v>43.5</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
-        <v>49.31</v>
+        <v>48.28</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>45.33</v>
+        <v>42.36</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>31.15</v>
+        <v>30.25</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>42.08</v>
+        <v>41.39</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
-        <v>50.22</v>
+        <v>51.96</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
-        <v>45.39</v>
+        <v>46.7</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3101,11 +3101,11 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>60.24</v>
+        <v>57.81</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -3133,7 +3133,7 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>41.81</v>
+        <v>41.13</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>51.14</v>
+        <v>47.12</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
-        <v>45.33</v>
+        <v>43.48</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
-        <v>45.41</v>
+        <v>43.85</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
-        <v>44.52</v>
+        <v>45.73</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>68.34999999999999</v>
+        <v>71.09</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3325,11 +3325,11 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>39.88</v>
+        <v>40.1</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>RSI &lt; 40</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -3357,7 +3357,7 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>48.46</v>
+        <v>46.58</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -3389,11 +3389,11 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>36.89</v>
+        <v>41.77</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>RSI &lt; 40</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -3421,11 +3421,11 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>41.31</v>
+        <v>39.99</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -3453,11 +3453,11 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>60.84</v>
+        <v>59.6</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -3485,7 +3485,7 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>47.19</v>
+        <v>45.75</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>58.86</v>
+        <v>57.8</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>43.8</v>
+        <v>50.96</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>45.22</v>
+        <v>45.09</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>55.47</v>
+        <v>53.15</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>60.65</v>
+        <v>60.46</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -3677,11 +3677,11 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>38.58</v>
+        <v>43.09</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>RSI &lt; 40</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -3709,7 +3709,7 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>62.1</v>
+        <v>61.15</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
-        <v>53.71</v>
+        <v>52.21</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
-        <v>55.07</v>
+        <v>52.31</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -3805,11 +3805,11 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
-        <v>60.88</v>
+        <v>59.09</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -3837,7 +3837,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
-        <v>51.56</v>
+        <v>51.76</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
-        <v>61.9</v>
+        <v>61.09</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
-        <v>50.91</v>
+        <v>49.77</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
-        <v>46.68</v>
+        <v>46.78</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
-        <v>64.15000000000001</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
-        <v>50.93</v>
+        <v>50.74</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
-        <v>72.92</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
-        <v>49.98</v>
+        <v>47.97</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
-        <v>43.12</v>
+        <v>41.01</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="n">
-        <v>56.11</v>
+        <v>57.54</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="n">
-        <v>44.37</v>
+        <v>42.45</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="n">
-        <v>42.49</v>
+        <v>40.73</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>64.53</v>
+        <v>63.3</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>43.51</v>
+        <v>42.39</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>59.75</v>
+        <v>55.58</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>45.54</v>
+        <v>45.79</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>67.64</v>
+        <v>66.03</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>54.92</v>
+        <v>52.06</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -4413,11 +4413,11 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>61.89</v>
+        <v>59.02</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -4445,7 +4445,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>54.21</v>
+        <v>51.31</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>58.67</v>
+        <v>55.7</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>56.24</v>
+        <v>57.3</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>68.20999999999999</v>
+        <v>68.66</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
-        <v>43.08</v>
+        <v>42</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
-        <v>69.08</v>
+        <v>66.28</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>47.09</v>
+        <v>46.87</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -4669,11 +4669,11 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="n">
-        <v>60.48</v>
+        <v>58.21</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="n">
-        <v>53.28</v>
+        <v>54.39</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="n">
-        <v>61.39</v>
+        <v>60.94</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="n">
-        <v>54.35</v>
+        <v>55.97</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="n">
-        <v>51.38</v>
+        <v>48.08</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="n">
-        <v>48.77</v>
+        <v>46.27</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="n">
-        <v>52.07</v>
+        <v>51.74</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
-        <v>57.48</v>
+        <v>58.1</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
-        <v>65.72</v>
+        <v>64.89</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="n">
-        <v>70.84999999999999</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="n">
-        <v>79.27</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>62.95</v>
+        <v>65.23</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>65.58</v>
+        <v>63.18</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="n">
-        <v>51.36</v>
+        <v>51.54</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>56.66</v>
+        <v>56.35</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>38.47</v>
+        <v>35.01</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>57</v>
+        <v>53.97</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
-        <v>73.64</v>
+        <v>74.06</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
-        <v>77.78</v>
+        <v>78.13</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
-        <v>59.77</v>
+        <v>59.79</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
-        <v>34.34</v>
+        <v>37.21</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -5341,11 +5341,11 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>60.69</v>
+        <v>57.27</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -5373,11 +5373,11 @@
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>59.31</v>
+        <v>61.45</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -5405,7 +5405,7 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>48.54</v>
+        <v>49.12</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
-        <v>61.36</v>
+        <v>62.65</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>37.43</v>
+        <v>38.39</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>65.52</v>
+        <v>62.73</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>65.81</v>
+        <v>66.39</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>48.79</v>
+        <v>48.25</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="n">
-        <v>55.32</v>
+        <v>56.68</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>45.44</v>
+        <v>42.45</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="n">
-        <v>55.15</v>
+        <v>56.78</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -5693,11 +5693,11 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
-        <v>61.07</v>
+        <v>59.56</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -5725,7 +5725,7 @@
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="n">
-        <v>47.91</v>
+        <v>44.98</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="n">
-        <v>44.33</v>
+        <v>42.67</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="n">
-        <v>50.08</v>
+        <v>48.72</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="n">
-        <v>48.28</v>
+        <v>46.96</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="n">
-        <v>59.34</v>
+        <v>56.46</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="n">
-        <v>54.13</v>
+        <v>53.72</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="n">
-        <v>52.69</v>
+        <v>50.74</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="n">
-        <v>53.81</v>
+        <v>54.5</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="n">
-        <v>49.35</v>
+        <v>50.78</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="n">
-        <v>42.72</v>
+        <v>40.52</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="n">
-        <v>50.69</v>
+        <v>51.36</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
-        <v>50.87</v>
+        <v>50.01</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>56.22</v>
+        <v>56.44</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
-        <v>49.89</v>
+        <v>46.79</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>44.3</v>
+        <v>44.52</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>40.76</v>
+        <v>40.33</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
-        <v>44.12</v>
+        <v>42.93</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>46.45</v>
+        <v>43.91</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="n">
-        <v>52.39</v>
+        <v>50.71</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="n">
-        <v>72.98999999999999</v>
+        <v>70.72</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -6365,11 +6365,11 @@
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>40.16</v>
+        <v>39.66</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -6397,7 +6397,7 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="n">
-        <v>65.51000000000001</v>
+        <v>65.44</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>47.33</v>
+        <v>47.39</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>51.44</v>
+        <v>48.37</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
-        <v>59</v>
+        <v>57.96</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -6525,11 +6525,11 @@
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="n">
-        <v>55.95</v>
+        <v>64.73</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -6557,7 +6557,7 @@
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="n">
-        <v>67.90000000000001</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="n">
-        <v>58.61</v>
+        <v>57.61</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="n">
-        <v>50.51</v>
+        <v>49.13</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="n">
-        <v>61.08</v>
+        <v>60.72</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="n">
-        <v>62.38</v>
+        <v>60.15</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="n">
-        <v>41.8</v>
+        <v>40.55</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="n">
-        <v>73.20999999999999</v>
+        <v>72.08</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="n">
-        <v>49.82</v>
+        <v>50.82</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="n">
-        <v>46.14</v>
+        <v>44.25</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="n">
-        <v>46.53</v>
+        <v>45.67</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="n">
-        <v>36.89</v>
+        <v>37.94</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="n">
-        <v>52.81</v>
+        <v>52.96</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="n">
-        <v>44.47</v>
+        <v>41.76</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="n">
-        <v>70.98999999999999</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>43.43</v>
+        <v>40.34</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>49.82</v>
+        <v>48.77</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="n">
-        <v>37.03</v>
+        <v>35.89</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="n">
-        <v>57.63</v>
+        <v>55.59</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="n">
-        <v>55.6</v>
+        <v>53.52</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>67.76000000000001</v>
+        <v>64.52</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="n">
-        <v>23.73</v>
+        <v>23.47</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="n">
-        <v>33.15</v>
+        <v>32.15</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="n">
-        <v>43.88</v>
+        <v>41.47</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="n">
-        <v>48.38</v>
+        <v>46.88</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="n">
-        <v>51.68</v>
+        <v>50.43</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>54.72</v>
+        <v>56.01</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="n">
-        <v>69.16</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="n">
-        <v>61.8</v>
+        <v>63.53</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -7604,7 +7604,11 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -7760,7 +7764,11 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -7838,7 +7846,11 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -7942,7 +7954,11 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -8072,7 +8088,11 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -8098,7 +8118,11 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -8410,7 +8434,11 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
@@ -8780,7 +8808,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bullish EMA Pullback</t>
+          <t>Bearish EMA Pullback</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -9042,11 +9070,7 @@
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
@@ -9124,7 +9148,11 @@
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
@@ -9696,11 +9724,7 @@
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
@@ -10436,7 +10460,11 @@
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
@@ -11034,7 +11062,11 @@
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
@@ -11086,7 +11118,11 @@
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
@@ -11532,7 +11568,11 @@
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
@@ -11792,7 +11832,11 @@
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
@@ -11922,7 +11966,11 @@
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
@@ -12082,7 +12130,11 @@
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
@@ -12134,7 +12186,11 @@
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
@@ -12398,7 +12454,11 @@
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
@@ -12450,7 +12510,11 @@
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
@@ -12528,7 +12592,11 @@
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
@@ -12866,7 +12934,11 @@
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
@@ -13366,7 +13438,11 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -13780,7 +13856,11 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -14604,11 +14684,7 @@
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
@@ -15552,7 +15628,11 @@
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
@@ -15898,11 +15978,7 @@
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
@@ -16540,11 +16616,7 @@
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
@@ -17044,11 +17116,7 @@
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
@@ -18936,7 +19004,11 @@
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
@@ -19018,11 +19090,7 @@
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
@@ -19138,7 +19206,11 @@
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
@@ -19368,10 +19440,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No scanner alerts detected for this interval</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -19381,7 +19457,11 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABIOCON</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19462,10 +19542,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No scanner alerts detected for this interval</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -19475,7 +19559,11 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKINDIA</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19838,20 +19926,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No scanner alerts detected for this interval</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>High Vol Expansion</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABIOCON</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19958,7 +20058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20026,7 +20126,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -20045,14 +20145,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHYUNDAI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGMRAIRPORT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -20071,14 +20171,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGMRAIRPORT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AWIPRO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -20097,14 +20197,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACHOLAFIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIGREEN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -20123,14 +20223,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AWIPRO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPOWER</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -20149,7 +20249,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATVSMOTOR</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACONCOR</t>
         </is>
       </c>
     </row>
@@ -20208,7 +20308,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NAM_INDIA</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -20227,14 +20327,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANAM_INDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALAURUSLABS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -20253,14 +20353,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHARATFORG</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOLYCAB</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -20279,59 +20379,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALAURUSLABS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>M&amp;M</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Bullish</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AM&amp;M</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Bullish</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKOTAKBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABIOCON</t>
         </is>
       </c>
     </row>
@@ -31980,7 +32028,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -32220,7 +32268,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -32400,7 +32448,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Weak Bearish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -32730,7 +32778,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Weak Bearish</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -33060,7 +33108,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -33120,7 +33168,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -33510,7 +33558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -33570,7 +33618,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -33600,7 +33648,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -33750,7 +33798,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -33960,7 +34008,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -34320,7 +34368,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Weak Bearish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -34350,7 +34398,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -34680,7 +34728,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -34710,7 +34758,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -34830,7 +34878,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -34920,7 +34968,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -35280,7 +35328,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -35400,7 +35448,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -35940,7 +35988,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -36030,7 +36078,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -36210,7 +36258,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Weak Bearish</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -36390,7 +36438,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -36450,7 +36498,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Weak Bearish</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -36540,7 +36588,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -36810,7 +36858,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -36870,7 +36918,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -36930,7 +36978,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -37470,7 +37518,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -37500,7 +37548,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -37590,7 +37638,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Weak Bearish</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -37980,7 +38028,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -38130,7 +38178,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -38190,7 +38238,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -38220,7 +38268,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Weak Bearish</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -44372,7 +44420,11 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -45694,11 +45746,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
@@ -50304,11 +50352,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
